--- a/artfynd/A 43007-2022 artfynd.xlsx
+++ b/artfynd/A 43007-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482966</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136482953</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482959</v>
       </c>
       <c r="B4" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
